--- a/CaseI.xlsx
+++ b/CaseI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\论文\02 Trans Smart Grid\00 程序汇总\Hydraulic-Transients-and-Thermal-Dynamics-Embedded-Contingency-Analysis-of-Integrated-Electricity-and-Heating-Systems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0755A7-55CE-48D5-A3B0-3D0C799792D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427CAC54-2E8F-40C3-A66D-56DEF63F42DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4230" windowWidth="16410" windowHeight="15345" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pipe" sheetId="5" r:id="rId1"/>
@@ -34,6 +34,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -213,7 +216,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0000_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -319,7 +322,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1981,5 +1984,6 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/CaseI.xlsx
+++ b/CaseI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\论文\02 Trans Smart Grid\00 程序汇总\Hydraulic-Transients-and-Thermal-Dynamics-Embedded-Contingency-Analysis-of-Integrated-Electricity-and-Heating-Systems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427CAC54-2E8F-40C3-A66D-56DEF63F42DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A680EE-E52E-4C58-B418-777D3C3BBE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4230" windowWidth="16410" windowHeight="15345" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pipe" sheetId="5" r:id="rId1"/>
@@ -241,6 +241,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -248,6 +249,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -260,6 +262,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1312,6 +1315,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2">
